--- a/Docs/assets to import - final from logistic Tripoli.xlsx
+++ b/Docs/assets to import - final from logistic Tripoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9EEC27-191F-4F80-8618-95C4603F94DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B135485C-F63C-463D-BA3C-0958501F21C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-36" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5749" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6030" uniqueCount="210">
   <si>
     <t>Furniture</t>
   </si>
@@ -664,6 +664,12 @@
   <si>
     <t>Malik`s Book shop</t>
   </si>
+  <si>
+    <t xml:space="preserve">Owned By </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B&amp;Z </t>
+  </si>
 </sst>
 </file>
 
@@ -1087,25 +1093,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W204"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X204"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1175,8 +1181,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1246,8 +1255,11 @@
       <c r="W2" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1317,8 +1329,11 @@
       <c r="W3" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1388,8 +1403,11 @@
       <c r="W4" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1459,8 +1477,11 @@
       <c r="W5" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1530,8 +1551,11 @@
       <c r="W6" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1601,8 +1625,11 @@
       <c r="W7" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1672,8 +1699,11 @@
       <c r="W8" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1743,8 +1773,11 @@
       <c r="W9" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1814,8 +1847,11 @@
       <c r="W10" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1883,8 +1919,11 @@
       <c r="W11" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1952,8 +1991,11 @@
       <c r="W12" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2021,8 +2063,11 @@
       <c r="W13" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2090,8 +2135,11 @@
       <c r="W14" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2159,8 +2207,11 @@
       <c r="W15" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2228,8 +2279,11 @@
       <c r="W16" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2297,8 +2351,11 @@
       <c r="W17" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2366,8 +2423,11 @@
       <c r="W18" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2435,8 +2495,11 @@
       <c r="W19" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2504,8 +2567,11 @@
       <c r="W20" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2573,8 +2639,11 @@
       <c r="W21" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2642,8 +2711,11 @@
       <c r="W22" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2711,8 +2783,11 @@
       <c r="W23" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2780,8 +2855,11 @@
       <c r="W24" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2849,8 +2927,11 @@
       <c r="W25" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2918,8 +2999,11 @@
       <c r="W26" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2987,8 +3071,11 @@
       <c r="W27" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3056,8 +3143,11 @@
       <c r="W28" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3125,8 +3215,11 @@
       <c r="W29" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3194,8 +3287,11 @@
       <c r="W30" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3263,8 +3359,11 @@
       <c r="W31" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3332,8 +3431,11 @@
       <c r="W32" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3401,8 +3503,11 @@
       <c r="W33" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3470,8 +3575,11 @@
       <c r="W34" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3539,8 +3647,11 @@
       <c r="W35" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3608,8 +3719,11 @@
       <c r="W36" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3677,8 +3791,11 @@
       <c r="W37" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3746,8 +3863,11 @@
       <c r="W38" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3815,8 +3935,11 @@
       <c r="W39" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3884,8 +4007,11 @@
       <c r="W40" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3953,8 +4079,11 @@
       <c r="W41" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4022,8 +4151,11 @@
       <c r="W42" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4091,8 +4223,11 @@
       <c r="W43" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4160,8 +4295,11 @@
       <c r="W44" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4229,8 +4367,11 @@
       <c r="W45" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4298,8 +4439,11 @@
       <c r="W46" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X46" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4367,8 +4511,11 @@
       <c r="W47" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4436,8 +4583,11 @@
       <c r="W48" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X48" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4505,8 +4655,11 @@
       <c r="W49" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4574,8 +4727,11 @@
       <c r="W50" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X50" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4643,8 +4799,11 @@
       <c r="W51" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X51" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4712,8 +4871,11 @@
       <c r="W52" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X52" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4781,8 +4943,11 @@
       <c r="W53" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X53" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4850,8 +5015,11 @@
       <c r="W54" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X54" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4919,8 +5087,11 @@
       <c r="W55" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X55" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4988,8 +5159,11 @@
       <c r="W56" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X56" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5057,8 +5231,11 @@
       <c r="W57" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X57" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5126,8 +5303,11 @@
       <c r="W58" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X58" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5195,8 +5375,11 @@
       <c r="W59" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X59" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5264,8 +5447,11 @@
       <c r="W60" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X60" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5333,8 +5519,11 @@
       <c r="W61" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X61" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5402,8 +5591,11 @@
       <c r="W62" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X62" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5471,8 +5663,11 @@
       <c r="W63" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X63" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5540,8 +5735,11 @@
       <c r="W64" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X64" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5609,8 +5807,11 @@
       <c r="W65" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X65" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5678,8 +5879,11 @@
       <c r="W66" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X66" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5747,8 +5951,11 @@
       <c r="W67" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X67" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5816,8 +6023,11 @@
       <c r="W68" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X68" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5885,8 +6095,11 @@
       <c r="W69" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X69" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5954,8 +6167,11 @@
       <c r="W70" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X70" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6023,8 +6239,11 @@
       <c r="W71" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X71" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6092,8 +6311,11 @@
       <c r="W72" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X72" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6161,8 +6383,11 @@
       <c r="W73" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X73" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6230,8 +6455,11 @@
       <c r="W74" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X74" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6299,8 +6527,11 @@
       <c r="W75" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X75" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6368,8 +6599,11 @@
       <c r="W76" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X76" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6437,8 +6671,11 @@
       <c r="W77" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X77" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6506,8 +6743,11 @@
       <c r="W78" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X78" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6574,8 +6814,11 @@
       <c r="W79" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X79" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6642,8 +6885,11 @@
       <c r="W80" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X80" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6710,8 +6956,11 @@
       <c r="W81" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X81" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6778,8 +7027,11 @@
       <c r="W82" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X82" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6846,8 +7098,11 @@
       <c r="W83" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X83" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6914,8 +7169,11 @@
       <c r="W84" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X84" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6982,8 +7240,11 @@
       <c r="W85" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X85" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7050,8 +7311,11 @@
       <c r="W86" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X86" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7118,8 +7382,11 @@
       <c r="W87" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X87" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7186,8 +7453,11 @@
       <c r="W88" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X88" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7254,8 +7524,11 @@
       <c r="W89" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X89" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7322,8 +7595,11 @@
       <c r="W90" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X90" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7390,8 +7666,11 @@
       <c r="W91" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X91" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7458,8 +7737,11 @@
       <c r="W92" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X92" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7526,8 +7808,11 @@
       <c r="W93" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X93" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7594,8 +7879,11 @@
       <c r="W94" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X94" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7662,8 +7950,11 @@
       <c r="W95" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X95" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7730,8 +8021,11 @@
       <c r="W96" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X96" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7798,8 +8092,11 @@
       <c r="W97" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X97" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7866,8 +8163,11 @@
       <c r="W98" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X98" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7934,8 +8234,11 @@
       <c r="W99" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X99" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8002,8 +8305,11 @@
       <c r="W100" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X100" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8070,8 +8376,11 @@
       <c r="W101" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X101" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8138,8 +8447,11 @@
       <c r="W102" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X102" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8206,8 +8518,11 @@
       <c r="W103" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X103" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8274,8 +8589,11 @@
       <c r="W104" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X104" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8342,8 +8660,11 @@
       <c r="W105" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X105" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8410,8 +8731,11 @@
       <c r="W106" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X106" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8478,8 +8802,11 @@
       <c r="W107" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X107" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8546,8 +8873,11 @@
       <c r="W108" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X108" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8614,8 +8944,11 @@
       <c r="W109" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X109" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8682,8 +9015,11 @@
       <c r="W110" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X110" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8750,8 +9086,11 @@
       <c r="W111" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X111" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8818,8 +9157,11 @@
       <c r="W112" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X112" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8886,8 +9228,11 @@
       <c r="W113" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X113" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8954,8 +9299,11 @@
       <c r="W114" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X114" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -9022,8 +9370,11 @@
       <c r="W115" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X115" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -9090,8 +9441,11 @@
       <c r="W116" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X116" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -9158,8 +9512,11 @@
       <c r="W117" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X117" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -9226,8 +9583,11 @@
       <c r="W118" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X118" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -9294,8 +9654,11 @@
       <c r="W119" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X119" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -9362,8 +9725,11 @@
       <c r="W120" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X120" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -9430,8 +9796,11 @@
       <c r="W121" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X121" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9498,8 +9867,11 @@
       <c r="W122" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X122" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -9566,8 +9938,11 @@
       <c r="W123" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X123" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -9634,8 +10009,11 @@
       <c r="W124" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X124" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -9702,8 +10080,11 @@
       <c r="W125" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X125" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9770,8 +10151,11 @@
       <c r="W126" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X126" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9838,8 +10222,11 @@
       <c r="W127" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X127" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -9906,8 +10293,11 @@
       <c r="W128" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X128" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9974,8 +10364,11 @@
       <c r="W129" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X129" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10042,8 +10435,11 @@
       <c r="W130" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X130" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10110,8 +10506,11 @@
       <c r="W131" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X131" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10178,8 +10577,11 @@
       <c r="W132" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X132" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10246,8 +10648,11 @@
       <c r="W133" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X133" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10314,8 +10719,11 @@
       <c r="W134" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X134" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10382,8 +10790,11 @@
       <c r="W135" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X135" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10450,8 +10861,11 @@
       <c r="W136" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X136" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10518,8 +10932,11 @@
       <c r="W137" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X137" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10586,8 +11003,11 @@
       <c r="W138" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X138" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10654,8 +11074,11 @@
       <c r="W139" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X139" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10722,8 +11145,11 @@
       <c r="W140" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X140" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10790,8 +11216,11 @@
       <c r="W141" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X141" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10858,8 +11287,11 @@
       <c r="W142" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X142" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10926,8 +11358,11 @@
       <c r="W143" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X143" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10994,8 +11429,11 @@
       <c r="W144" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X144" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11062,8 +11500,11 @@
       <c r="W145" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X145" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11130,8 +11571,11 @@
       <c r="W146" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X146" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11198,8 +11642,11 @@
       <c r="W147" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X147" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11266,8 +11713,11 @@
       <c r="W148" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X148" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11334,8 +11784,11 @@
       <c r="W149" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X149" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11402,8 +11855,11 @@
       <c r="W150" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X150" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11470,8 +11926,11 @@
       <c r="W151" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X151" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11538,8 +11997,11 @@
       <c r="W152" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X152" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11606,8 +12068,11 @@
       <c r="W153" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X153" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11674,8 +12139,11 @@
       <c r="W154" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X154" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11742,8 +12210,11 @@
       <c r="W155" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X155" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11810,8 +12281,11 @@
       <c r="W156" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X156" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11878,8 +12352,11 @@
       <c r="W157" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X157" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11946,8 +12423,11 @@
       <c r="W158" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X158" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -12014,8 +12494,11 @@
       <c r="W159" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X159" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -12082,8 +12565,11 @@
       <c r="W160" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X160" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -12150,8 +12636,11 @@
       <c r="W161" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X161" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -12218,8 +12707,11 @@
       <c r="W162" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X162" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -12286,8 +12778,11 @@
       <c r="W163" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X163" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -12354,8 +12849,11 @@
       <c r="W164" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X164" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -12422,8 +12920,11 @@
       <c r="W165" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X165" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -12490,8 +12991,11 @@
       <c r="W166" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X166" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -12558,8 +13062,11 @@
       <c r="W167" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X167" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -12626,8 +13133,11 @@
       <c r="W168" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X168" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -12694,8 +13204,11 @@
       <c r="W169" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X169" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -12762,8 +13275,11 @@
       <c r="W170" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X170" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -12830,8 +13346,11 @@
       <c r="W171" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X171" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -12898,8 +13417,11 @@
       <c r="W172" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X172" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -12966,8 +13488,11 @@
       <c r="W173" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X173" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>184</v>
       </c>
@@ -13034,8 +13559,11 @@
       <c r="W174" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X174" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>185</v>
       </c>
@@ -13102,8 +13630,11 @@
       <c r="W175" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X175" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>186</v>
       </c>
@@ -13170,8 +13701,11 @@
       <c r="W176" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X176" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>187</v>
       </c>
@@ -13238,8 +13772,11 @@
       <c r="W177" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X177" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>188</v>
       </c>
@@ -13306,8 +13843,11 @@
       <c r="W178" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X178" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>189</v>
       </c>
@@ -13374,8 +13914,11 @@
       <c r="W179" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X179" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>190</v>
       </c>
@@ -13442,8 +13985,11 @@
       <c r="W180" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X180" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>191</v>
       </c>
@@ -13510,8 +14056,11 @@
       <c r="W181" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X181" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>192</v>
       </c>
@@ -13578,8 +14127,11 @@
       <c r="W182" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X182" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>193</v>
       </c>
@@ -13646,8 +14198,11 @@
       <c r="W183" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X183" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>194</v>
       </c>
@@ -13714,8 +14269,11 @@
       <c r="W184" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X184" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>195</v>
       </c>
@@ -13782,8 +14340,11 @@
       <c r="W185" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X185" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>196</v>
       </c>
@@ -13850,8 +14411,11 @@
       <c r="W186" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X186" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>197</v>
       </c>
@@ -13918,8 +14482,11 @@
       <c r="W187" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X187" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>198</v>
       </c>
@@ -13986,8 +14553,11 @@
       <c r="W188" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X188" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>229</v>
       </c>
@@ -14054,8 +14624,11 @@
       <c r="W189" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X189" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>231</v>
       </c>
@@ -14122,8 +14695,11 @@
       <c r="W190" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X190" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>232</v>
       </c>
@@ -14190,8 +14766,11 @@
       <c r="W191" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X191" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>233</v>
       </c>
@@ -14258,8 +14837,11 @@
       <c r="W192" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X192" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>234</v>
       </c>
@@ -14326,8 +14908,11 @@
       <c r="W193" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X193" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>235</v>
       </c>
@@ -14394,8 +14979,11 @@
       <c r="W194" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X194" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>236</v>
       </c>
@@ -14462,8 +15050,11 @@
       <c r="W195" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X195" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>237</v>
       </c>
@@ -14530,8 +15121,11 @@
       <c r="W196" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X196" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>238</v>
       </c>
@@ -14598,8 +15192,11 @@
       <c r="W197" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X197" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -14666,8 +15263,11 @@
       <c r="W198" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X198" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>240</v>
       </c>
@@ -14734,8 +15334,11 @@
       <c r="W199" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X199" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="N204" s="12"/>
     </row>
   </sheetData>
@@ -14761,24 +15364,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}">
-  <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -14848,8 +15451,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>173</v>
       </c>
@@ -14917,8 +15523,11 @@
       <c r="W2" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>174</v>
       </c>
@@ -14986,8 +15595,11 @@
       <c r="W3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>175</v>
       </c>
@@ -15055,8 +15667,11 @@
       <c r="W4" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>176</v>
       </c>
@@ -15124,8 +15739,11 @@
       <c r="W5" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>177</v>
       </c>
@@ -15193,8 +15811,11 @@
       <c r="W6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>178</v>
       </c>
@@ -15262,8 +15883,11 @@
       <c r="W7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>179</v>
       </c>
@@ -15331,8 +15955,11 @@
       <c r="W8" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>180</v>
       </c>
@@ -15399,8 +16026,11 @@
       <c r="W9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>181</v>
       </c>
@@ -15467,8 +16097,11 @@
       <c r="W10" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>182</v>
       </c>
@@ -15535,8 +16168,11 @@
       <c r="W11" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>183</v>
       </c>
@@ -15603,8 +16239,11 @@
       <c r="W12" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>199</v>
       </c>
@@ -15671,8 +16310,11 @@
       <c r="W13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>200</v>
       </c>
@@ -15739,8 +16381,11 @@
       <c r="W14" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>201</v>
       </c>
@@ -15807,8 +16452,11 @@
       <c r="W15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>202</v>
       </c>
@@ -15875,8 +16523,11 @@
       <c r="W16" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>203</v>
       </c>
@@ -15943,8 +16594,11 @@
       <c r="W17" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>204</v>
       </c>
@@ -16011,8 +16665,11 @@
       <c r="W18" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>205</v>
       </c>
@@ -16079,8 +16736,11 @@
       <c r="W19" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>206</v>
       </c>
@@ -16147,8 +16807,11 @@
       <c r="W20" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>207</v>
       </c>
@@ -16215,8 +16878,11 @@
       <c r="W21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>208</v>
       </c>
@@ -16283,8 +16949,11 @@
       <c r="W22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>209</v>
       </c>
@@ -16351,8 +17020,11 @@
       <c r="W23" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>210</v>
       </c>
@@ -16419,8 +17091,11 @@
       <c r="W24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>211</v>
       </c>
@@ -16487,8 +17162,11 @@
       <c r="W25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>212</v>
       </c>
@@ -16555,8 +17233,11 @@
       <c r="W26" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>213</v>
       </c>
@@ -16623,8 +17304,11 @@
       <c r="W27" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>215</v>
       </c>
@@ -16691,8 +17375,11 @@
       <c r="W28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>216</v>
       </c>
@@ -16759,8 +17446,11 @@
       <c r="W29" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>217</v>
       </c>
@@ -16827,8 +17517,11 @@
       <c r="W30" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>218</v>
       </c>
@@ -16895,8 +17588,11 @@
       <c r="W31" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>219</v>
       </c>
@@ -16963,8 +17659,11 @@
       <c r="W32" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>220</v>
       </c>
@@ -17031,8 +17730,11 @@
       <c r="W33" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>221</v>
       </c>
@@ -17099,8 +17801,11 @@
       <c r="W34" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>222</v>
       </c>
@@ -17167,8 +17872,11 @@
       <c r="W35" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>223</v>
       </c>
@@ -17235,8 +17943,11 @@
       <c r="W36" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>224</v>
       </c>
@@ -17303,8 +18014,11 @@
       <c r="W37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>225</v>
       </c>
@@ -17371,8 +18085,11 @@
       <c r="W38" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>226</v>
       </c>
@@ -17439,8 +18156,11 @@
       <c r="W39" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>227</v>
       </c>
@@ -17507,8 +18227,11 @@
       <c r="W40" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>228</v>
       </c>
@@ -17575,8 +18298,11 @@
       <c r="W41" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>230</v>
       </c>
@@ -17643,8 +18369,11 @@
       <c r="W42" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>241</v>
       </c>
@@ -17711,8 +18440,11 @@
       <c r="W43" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>242</v>
       </c>
@@ -17779,8 +18511,11 @@
       <c r="W44" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>243</v>
       </c>
@@ -17846,6 +18581,9 @@
       </c>
       <c r="W45" t="s">
         <v>82</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -17871,23 +18609,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087FDD54-5E17-401C-A88E-55822B904567}">
-  <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -17957,8 +18695,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>214</v>
       </c>
@@ -18024,6 +18765,9 @@
       </c>
       <c r="W2" t="s">
         <v>26</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -18033,17 +18777,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45841932-2100-4D5F-A69E-818128AA5E3E}">
-  <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -18125,8 +18869,11 @@
       <c r="AA1" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -18206,15 +18953,18 @@
       <c r="AA2" t="e">
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="G3" s="9"/>
       <c r="I3" s="8"/>
       <c r="O3" s="11"/>
       <c r="T3" s="7"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="G4" s="9"/>
       <c r="I4" s="8"/>
       <c r="T4" s="7"/>
@@ -18244,24 +18994,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46FE8D-6B9D-4019-AD13-4A9515E01ECE}">
-  <dimension ref="A1:U33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -18325,8 +19075,11 @@
       <c r="U1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -18375,8 +19128,11 @@
       <c r="U2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -18425,8 +19181,11 @@
       <c r="U3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -18475,8 +19234,11 @@
       <c r="U4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -18525,8 +19287,11 @@
       <c r="U5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -18575,8 +19340,11 @@
       <c r="U6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -18625,8 +19393,11 @@
       <c r="U7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V7" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -18675,8 +19446,11 @@
       <c r="U8" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -18725,8 +19499,11 @@
       <c r="U9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -18775,8 +19552,11 @@
       <c r="U10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -18825,8 +19605,11 @@
       <c r="U11" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -18875,8 +19658,11 @@
       <c r="U12" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -18925,8 +19711,11 @@
       <c r="U13" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -18975,8 +19764,11 @@
       <c r="U14" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -19025,8 +19817,11 @@
       <c r="U15" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -19075,8 +19870,11 @@
       <c r="U16" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -19125,8 +19923,11 @@
       <c r="U17" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -19175,8 +19976,11 @@
       <c r="U18" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -19225,8 +20029,11 @@
       <c r="U19" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -19275,8 +20082,11 @@
       <c r="U20" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -19325,8 +20135,11 @@
       <c r="U21" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -19375,8 +20188,11 @@
       <c r="U22" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -19425,8 +20241,11 @@
       <c r="U23" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V23" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -19475,8 +20294,11 @@
       <c r="U24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -19525,8 +20347,11 @@
       <c r="U25" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V25" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -19575,8 +20400,11 @@
       <c r="U26" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -19625,8 +20453,11 @@
       <c r="U27" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V27" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -19675,8 +20506,11 @@
       <c r="U28" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -19725,8 +20559,11 @@
       <c r="U29" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V29" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -19775,8 +20612,11 @@
       <c r="U30" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V30" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -19825,8 +20665,11 @@
       <c r="U31" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V31" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -19875,8 +20718,11 @@
       <c r="U32" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -19924,6 +20770,9 @@
       </c>
       <c r="U33" t="s">
         <v>148</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -19934,14 +20783,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB899B9E-9D29-4608-AC57-3843A909BED5}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -20011,15 +20860,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D0FD15-6627-45B8-AE32-055E4B703EE2}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
